--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.14832025343094</v>
+        <v>2.624102041182528</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56390433885424</v>
+        <v>2.854134455063815</v>
       </c>
       <c r="E2" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F2" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.911579470259685</v>
+        <v>0.6356316639171988</v>
       </c>
       <c r="D3" t="n">
-        <v>5.197955647543775</v>
+        <v>0.8446677927258636</v>
       </c>
       <c r="E3" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F3" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.11346350864656</v>
+        <v>1.968437820155066</v>
       </c>
       <c r="D4" t="n">
-        <v>13.17547389071445</v>
+        <v>2.141014507241098</v>
       </c>
       <c r="E4" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F4" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.54378275975664</v>
+        <v>3.338364698460454</v>
       </c>
       <c r="D5" t="n">
-        <v>13.38427767527591</v>
+        <v>2.174945122232335</v>
       </c>
       <c r="E5" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F5" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.8266966241427</v>
+        <v>4.846838201423189</v>
       </c>
       <c r="D6" t="n">
-        <v>22.08632055267595</v>
+        <v>3.589027089809842</v>
       </c>
       <c r="E6" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F6" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.55875120608651</v>
+        <v>5.453297070989057</v>
       </c>
       <c r="D7" t="n">
-        <v>33.31798675405375</v>
+        <v>5.414172847533735</v>
       </c>
       <c r="E7" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F7" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.37813438323458</v>
+        <v>6.56144683727562</v>
       </c>
       <c r="D8" t="n">
-        <v>32.42255730540425</v>
+        <v>5.268665562128191</v>
       </c>
       <c r="E8" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F8" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50711110085584</v>
+        <v>4.957405553889075</v>
       </c>
       <c r="D9" t="n">
-        <v>29.27888342063483</v>
+        <v>4.75781855585316</v>
       </c>
       <c r="E9" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F9" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.04930884961203</v>
+        <v>3.095512688061955</v>
       </c>
       <c r="D10" t="n">
-        <v>18.94632488144638</v>
+        <v>3.078777793235037</v>
       </c>
       <c r="E10" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F10" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.285418212309878</v>
+        <v>1.183880459500355</v>
       </c>
       <c r="D11" t="n">
-        <v>7.036091916307856</v>
+        <v>1.143364936400027</v>
       </c>
       <c r="E11" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F11" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.19910351379808</v>
+        <v>5.882354320992188</v>
       </c>
       <c r="D12" t="n">
-        <v>35.01256781615576</v>
+        <v>5.689542270125311</v>
       </c>
       <c r="E12" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F12" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.99338836975376</v>
+        <v>2.598925610084986</v>
       </c>
       <c r="D13" t="n">
-        <v>16.21947569492924</v>
+        <v>2.635664800426002</v>
       </c>
       <c r="E13" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F13" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.95923101604739</v>
+        <v>4.705875040107702</v>
       </c>
       <c r="D14" t="n">
-        <v>27.85763179307818</v>
+        <v>4.526865166375205</v>
       </c>
       <c r="E14" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F14" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66467973893406</v>
+        <v>4.658010457576785</v>
       </c>
       <c r="D15" t="n">
-        <v>27.94703445518578</v>
+        <v>4.541393098967689</v>
       </c>
       <c r="E15" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F15" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.35087393207688</v>
+        <v>4.607017013962493</v>
       </c>
       <c r="D16" t="n">
-        <v>19.0261820744102</v>
+        <v>3.091754587091657</v>
       </c>
       <c r="E16" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F16" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.76485022091617</v>
+        <v>5.486788160898878</v>
       </c>
       <c r="D17" t="n">
-        <v>23.71388830842519</v>
+        <v>3.853506850119094</v>
       </c>
       <c r="E17" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F17" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.41346060354158</v>
+        <v>6.079687348075507</v>
       </c>
       <c r="D18" t="n">
-        <v>32.81781516998999</v>
+        <v>5.332894965123374</v>
       </c>
       <c r="E18" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F18" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.84512703476944</v>
+        <v>7.124833143150035</v>
       </c>
       <c r="D19" t="n">
-        <v>44.18542833042411</v>
+        <v>7.180132103693918</v>
       </c>
       <c r="E19" t="n">
-        <v>11.15386039318253</v>
+        <v>1.812502313892161</v>
       </c>
       <c r="F19" t="n">
-        <v>10.11213255458883</v>
+        <v>1.643221540120685</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
